--- a/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éva est à la maison. Maman ouvre la porte du balcon. L'air sent le thym. Éva reste avec l'adulte. Maman dit : on reste derrière la protection. Éva pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Éva pose les mains sur la protection. Elle reste derrière la protection. Un oiseau chante. Éva dit : maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.</t>
+          <t>Éva est à la maison. Maman ouvre la porte du balcon. L'air sent le thym. Éva reste avec l'adulte. On reste derrière la protection. Éva pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Éva pose les mains sur la protection. Elle reste derrière la protection. Un oiseau chante. Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Éva est à la maison. Maman ouvre la porte du balcon. L'air sent le thym. Éva reste avec l'adulte.
+maman|On reste derrière la protection.
+narrateur|Éva pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Éva pose les mains sur la protection. Elle reste derrière la protection. Un oiseau chante.
+enfant-f|Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Éva est au balcon. Que fait-elle ?</t>
         </is>
       </c>
     </row>
@@ -1641,6 +1670,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Éva a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1807,6 +1841,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Éva et maman rentrent. Les pieds restent au sol.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1969,6 +2008,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1987,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2004,6 +2048,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,11 @@
 enfant-f|Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Éva est au balcon. Que fait-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1675,6 +1686,7 @@
           <t>narrateur|Éva a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1846,6 +1858,7 @@
           <t>narrateur|Éva et maman rentrent. Les pieds restent au sol.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2013,6 +2026,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2031,7 +2045,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2055,6 +2069,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2256,6 +2284,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Éva au balcon avec maman</t>
+          <t>Le moulin de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un petit moulin en papier tourne. Sarah va au balcon avec maman. Elles nomment les nuages. Pieds au sol, derrière la protection.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Éva est à la maison. Maman ouvre la porte du balcon. L'air sent le thym. Éva reste avec l'adulte. On reste derrière la protection. Éva pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Éva pose les mains sur la protection. Elle reste derrière la protection. Un oiseau chante. Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.</t>
+          <t>Un petit moulin en papier tourne. Il est rouge et jaune. Le vent le pousse, tout doux. Ça fait un bruit de papier, tout fin. Les dalles sont fraîches sous les chaussons. Ça sent le thym, près de la porte. Une clochette de vélo sonne, tout loin. Le bâton du moulin est lisse. Tu as vu le moulin, Sarah ? Oui, maman. Il tourne. Le vent est gentil, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent le thym, plus fort. Sarah reste avec l'adulte. On reste derrière la protection. D'accord, maman. Sarah pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Sarah pose les mains sur la protection. Elle reste derrière la protection. Bravo, Sarah. Tes pieds sont au sol. Un oiseau chante, tout haut. Maman, l'oiseau. Je l'entends. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Sarah est calme. L'adulte nomme les nuages. Celui-là est tout rond. Comme un mouton. Oui. Un petit mouton blanc. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Elles respirent. C'est doux. Tu as fini de regarder le nuage ? Encore un peu. Encore un peu, d'accord. Le moulin tourne encore. Les pieds restent au sol. Tu entends le vélo, tout loin ? Oui. Ding. On l'écoute ici.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,63 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Éva est à la maison. Maman ouvre la porte du balcon. L'air sent le thym. Éva reste avec l'adulte.
+          <t>narrateur|Un petit moulin en papier tourne.
+narrateur|Il est rouge et jaune.
+narrateur|Le vent le pousse, tout doux.
+narrateur|Ça fait un bruit de papier, tout fin.
+narrateur|Les dalles sont fraîches sous les chaussons.
+narrateur|Ça sent le thym, près de la porte.
+narrateur|Une clochette de vélo sonne, tout loin.
+narrateur|Le bâton du moulin est lisse.
+maman|Tu as vu le moulin, Sarah ?
+enfant-f|Oui, maman.
+enfant-f|Il tourne.
+maman|Le vent est gentil, aujourd'hui.
+narrateur|En ce moment, maman ouvre la porte.
+narrateur|L'air sent le thym, plus fort.
+narrateur|Sarah reste avec l'adulte.
 maman|On reste derrière la protection.
-narrateur|Éva pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Éva pose les mains sur la protection. Elle reste derrière la protection. Un oiseau chante.
-enfant-f|Maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.</t>
+enfant-f|D'accord, maman.
+narrateur|Sarah pose les pieds au sol.
+narrateur|Les pieds restent au sol.
+narrateur|Elle sent les dalles sous les chaussons.
+narrateur|La protection est devant elle.
+narrateur|Sarah pose les mains sur la protection.
+narrateur|Elle reste derrière la protection.
+maman|Bravo, Sarah.
+maman|Tes pieds sont au sol.
+narrateur|Un oiseau chante, tout haut.
+enfant-f|Maman, l'oiseau.
+maman|Je l'entends.
+maman|On le regarde ici, avec moi.
+narrateur|Maman est près d'elle.
+narrateur|Parce que les pieds sont au sol, Sarah est calme.
+narrateur|L'adulte nomme les nuages.
+maman|Celui-là est tout rond.
+enfant-f|Comme un mouton.
+maman|Oui.
+maman|Un petit mouton blanc.
+maman|On reste avec l'adulte.
+maman|Derrière la protection.
+enfant-f|Pieds au sol.
+maman|Oui.
+maman|C'est du bon travail.
+narrateur|Elles respirent.
+narrateur|C'est doux.
+maman|Tu as fini de regarder le nuage ?
+enfant-f|Encore un peu.
+maman|Encore un peu, d'accord.
+narrateur|Le moulin tourne encore.
+narrateur|Les pieds restent au sol.
+maman|Tu entends le vélo, tout loin ?
+enfant-f|Oui.
+enfant-f|Ding.
+maman|On l'écoute ici.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>enfants_parc</t>
+          <t>vent,oiseau</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Éva est au balcon. Que fait-elle ?</t>
+          <t>Sarah est au balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1507,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Éva est au balcon. Que fait-elle ?</t>
+          <t>narrateur|Sarah est au balcon.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1535,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Éva a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
+          <t>Sarah a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Sarah. Pieds au sol. Avec maman. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1683,7 +1744,16 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Éva a les pieds au sol. Elle est derrière la protection. Maman, l'adulte, est là.</t>
+          <t>narrateur|Sarah a les pieds au sol.
+narrateur|Elle est derrière la protection.
+maman|Tu es avec l'adulte.
+maman|Bravo, Sarah.
+enfant-f|Pieds au sol.
+enfant-f|Avec maman.
+maman|Oui.
+maman|C'est du bon travail.
+maman|Tu restes derrière la protection ?
+enfant-f|Oui, maman.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1711,7 +1781,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Éva et maman rentrent. Les pieds restent au sol.</t>
+          <t>Sarah et maman rentrent. Les pieds restent au sol. Le moulin tourne plus doucement. On le laisse au vent ? Oui, maman. Tu as les pieds au sol, encore. Bravo. Le nuage était un mouton. On l'a nommé ensemble. Derrière la protection. Tu veux le moulin près de la fenêtre ? Oui. Le papier est encore un peu frais. On était avec l'adulte.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1855,7 +1925,20 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Éva et maman rentrent. Les pieds restent au sol.</t>
+          <t>narrateur|Sarah et maman rentrent.
+narrateur|Les pieds restent au sol.
+narrateur|Le moulin tourne plus doucement.
+maman|On le laisse au vent ?
+enfant-f|Oui, maman.
+maman|Tu as les pieds au sol, encore.
+maman|Bravo.
+enfant-f|Le nuage était un mouton.
+maman|On l'a nommé ensemble.
+maman|Derrière la protection.
+maman|Tu veux le moulin près de la fenêtre ?
+enfant-f|Oui.
+narrateur|Le papier est encore un peu frais.
+maman|On était avec l'adulte.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1883,7 +1966,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Tu as fait du bon travail. Le petit moulin s'arrête. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2023,7 +2106,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'avais les pieds au sol.
+enfant-f|Avec maman.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le petit moulin s'arrête.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2045,7 +2133,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2083,6 +2171,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un petit moulin en papier tourne. Il est rouge et jaune. Le vent le pousse, tout doux. Ça fait un bruit de papier, tout fin. Les dalles sont fraîches sous les chaussons. Ça sent le thym, près de la porte. Une clochette de vélo sonne, tout loin. Le bâton du moulin est lisse. Tu as vu le moulin, Sarah ? Oui, maman. Il tourne. Le vent est gentil, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent le thym, plus fort. Sarah reste avec l'adulte. On reste derrière la protection. D'accord, maman. Sarah pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Sarah pose les mains sur la protection. Elle reste derrière la protection. Bravo, Sarah. Tes pieds sont au sol. Un oiseau chante, tout haut. Maman, l'oiseau. Je l'entends. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Sarah est calme. L'adulte nomme les nuages. Celui-là est tout rond. Comme un mouton. Oui. Un petit mouton blanc. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. C'est du bon travail. Elles respirent. C'est doux. Tu as fini de regarder le nuage ? Encore un peu. Encore un peu, d'accord. Le moulin tourne encore. Les pieds restent au sol. Tu entends le vélo, tout loin ? Oui. Ding. On l'écoute ici.</t>
+          <t>Un petit moulin en papier tourne. Il est rouge et jaune. Le vent le pousse, tout doux. Ça fait un bruit de papier, tout fin. Les dalles sont fraîches sous les chaussons. Ça sent le thym, près de la porte. Une clochette de vélo sonne, tout loin. Le bâton du moulin est lisse. Tu as vu le moulin, Sarah ? Oui, maman. Il tourne. Le vent est gentil, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent le thym, plus fort. Sarah reste avec l'adulte. On reste derrière la protection. D'accord, maman. Sarah pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Sarah pose les mains sur la protection. Elle reste derrière la protection. Bravo, Sarah. Tes pieds sont au sol. Un oiseau chante, tout haut. Maman, l'oiseau. Je l'entends. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Sarah est calme. L'adulte nomme les nuages. Celui-là est tout rond. Comme un mouton. Oui. Un petit mouton blanc. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. Elles respirent. C'est doux. Tu as fini de regarder le nuage ? Encore un peu. Encore un peu, d'accord. Le moulin tourne encore. Les pieds restent au sol. Tu entends le vélo, tout loin ? Oui. Ding. On l'écoute ici.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Éva est à la maison. Maman ouvre la porte du balcon. L'air sent le thym. Éva reste avec l'adulte. Maman dit : on reste derrière la protection. Éva pose les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Éva pose les mains sur la protection. Elle reste derrière la protection. Un oiseau chante. Éva dit : maman, l'oiseau. Maman est près d'elle. Parce que les pieds sont au sol, Éva est calme. L'adulte nomme les nuages. Elles respirent. C'est doux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un petit moulin en papier tourne. Il est rouge et jaune. Le vent le pousse, tout doux. Ça fait un bruit de papier, tout fin. Les dalles sont fraîches sous les chaussons. Ça sent le thym, près de la porte. Une clochette de vélo sonne, tout loin. Le bâton du moulin est lisse. Tu as vu le moulin, Sarah ? Oui, maman. Il tourne. Le vent est gentil, aujourd'hui. En ce moment, maman ouvre la porte. L'air sent le thym, plus fort. Sarah reste avec l'adulte. On reste derrière la protection. D'accord, maman. Sarah pose les pieds au sol. Les pieds restent au sol. Elle sent les dalles sous les chaussons. La protection est devant elle. Sarah pose les mains sur la protection. Elle reste derrière la protection. Bravo, Sarah. Tes pieds sont au sol. Un oiseau chante, tout haut. Maman, l'oiseau. Je l'entends. On le regarde ici, avec moi. Maman est près d'elle. Parce que les pieds sont au sol, Sarah est calme. L'adulte nomme les nuages. Celui-là est tout rond. Comme un mouton. Oui. Un petit mouton blanc. On reste avec l'adulte. Derrière la protection. Pieds au sol. Oui. Elles respirent. C'est doux. Tu as fini de regarder le nuage ? Encore un peu. Encore un peu, d'accord. Le moulin tourne encore. Les pieds restent au sol. Tu entends le vélo, tout loin ? Oui. Ding. On l'écoute ici.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1364,7 +1364,6 @@
 maman|Derrière la protection.
 enfant-f|Pieds au sol.
 maman|Oui.
-maman|C'est du bon travail.
 narrateur|Elles respirent.
 narrateur|C'est doux.
 maman|Tu as fini de regarder le nuage ?
@@ -1412,7 +1411,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éva est au balcon. Que fait-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah est au balcon. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1570,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1596,12 +1594,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Sarah. Pieds au sol. Avec maman. Oui. C'est du bon travail. Tu restes derrière la protection ? Oui, maman.</t>
+          <t>Sarah a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Sarah. Pieds au sol. Avec maman. Oui. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éva a les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; au sol. Elle est derrière la protection. Maman, l'adulte, est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a les pieds au sol. Elle est derrière la protection. Tu es avec l'adulte. Bravo, Sarah. Pieds au sol. Avec maman. Oui. Tu restes derrière la protection ? Oui, maman.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,12 +1749,10 @@
 enfant-f|Pieds au sol.
 enfant-f|Avec maman.
 maman|Oui.
-maman|C'est du bon travail.
 maman|Tu restes derrière la protection ?
 enfant-f|Oui, maman.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1786,7 +1782,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;Éva et maman rentrent. Les &lt;emphasis level="moderate"&gt;pieds&lt;/emphasis&gt; restent au sol.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah et maman rentrent. Les pieds restent au sol. Le moulin tourne plus doucement. On le laisse au vent ? Oui, maman. Tu as les pieds au sol, encore. Bravo. Le nuage était un mouton. On l'a nommé ensemble. Derrière la protection. Tu veux le moulin près de la fenêtre ? Oui. Le papier est encore un peu frais. On était avec l'adulte.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1941,7 +1937,6 @@
 maman|On était avec l'adulte.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1966,12 +1961,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'avais les pieds au sol. Avec maman. Bravo. Tu as fait du bon travail. Le petit moulin s'arrête. L'histoire est finie.</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Le petit moulin s'arrête.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'avais les pieds au sol. Avec maman. Bravo. Le petit moulin s'arrête.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2109,12 +2104,9 @@
           <t>enfant-f|J'avais les pieds au sol.
 enfant-f|Avec maman.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le petit moulin s'arrête.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le petit moulin s'arrête.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2133,7 +2125,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2178,6 +2170,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
+++ b/stories/arbres/ATOM-SEC.MAI.003-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Éva, maman</t>
+          <t>Sarah, maman</t>
         </is>
       </c>
     </row>
